--- a/nriss-patch-2/ig/observations-summary.xlsx
+++ b/nriss-patch-2/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="67">
   <si>
     <t>Profile</t>
   </si>
@@ -164,7 +164,7 @@
     <t>Observation - FR Observation Radiation Exposure Document</t>
   </si>
   <si>
-    <t>LOINC#73569-6</t>
+    <t>null#73569-6</t>
   </si>
   <si>
     <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
@@ -179,7 +179,7 @@
     <t>Observation Category Codes#social-history</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-social-history-code-cisis|20260619134042 (required)</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-social-history-code-cisis|20260916095455 (required)</t>
   </si>
   <si>
     <t>fr-observation-vital-signs-document</t>
@@ -191,7 +191,7 @@
     <t>Observation Category Codes#vital-signs</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis|20260619134043 (required)</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis|20260916095457 (required)</t>
   </si>
   <si>
     <t>fr-observation-vital-signs-panel-document</t>
@@ -346,7 +346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -456,10 +456,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>13</v>
@@ -468,16 +468,16 @@
         <v>13</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>17</v>
@@ -491,10 +491,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>13</v>
@@ -503,16 +503,16 @@
         <v>13</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
@@ -526,10 +526,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>13</v>
@@ -538,16 +538,16 @@
         <v>13</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>27</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>17</v>
@@ -561,10 +561,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>13</v>
@@ -573,16 +573,16 @@
         <v>13</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -596,10 +596,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>13</v>
@@ -608,16 +608,16 @@
         <v>13</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>17</v>
@@ -631,10 +631,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>13</v>
@@ -643,16 +643,16 @@
         <v>13</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>17</v>
@@ -666,10 +666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>13</v>
@@ -678,16 +678,16 @@
         <v>13</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>26</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>17</v>
@@ -701,28 +701,28 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>15</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>17</v>
@@ -736,28 +736,28 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>39</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>17</v>
@@ -771,28 +771,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>17</v>
@@ -806,28 +806,28 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -836,76 +836,6 @@
         <v>13</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="F15" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="F16" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K16" t="s" s="2">
         <v>13</v>
       </c>
     </row>
